--- a/Screen_4_Exclude_PEC_NonPeerReviewed/validation_data/stage_4_validation_workbook_50.xlsx
+++ b/Screen_4_Exclude_PEC_NonPeerReviewed/validation_data/stage_4_validation_workbook_50.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nhs-my.sharepoint.com/personal/oliver_carey1_nhs_net/Documents/Documents/Projects/NHSCRB/Screen_4_Exclude_PEC_NonPeerReviewed/validation_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{193B0AB5-D142-4433-B571-1B09E36D9344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DFCD493-DA62-46B2-84E4-09B8B141996A}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{193B0AB5-D142-4433-B571-1B09E36D9344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B54319B6-22AD-4C74-BB6C-215F5FFA5A7E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{66513E08-89B8-4D61-A86D-819C01466699}"/>
   </bookViews>
@@ -899,6 +899,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3893,7 +3897,6 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1235A4A9-643F-403F-8F39-91437DA8F632}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:K42"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -3932,7 +3935,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -3967,7 +3970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -4002,7 +4005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -4037,7 +4040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -4107,7 +4110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -4142,7 +4145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -4177,7 +4180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -4212,7 +4215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -4247,7 +4250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -4317,7 +4320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -4352,7 +4355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -4387,7 +4390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -4422,7 +4425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -4457,7 +4460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>47</v>
       </c>
@@ -4492,7 +4495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>49</v>
       </c>
@@ -4527,7 +4530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -4562,7 +4565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>57</v>
       </c>
@@ -4597,7 +4600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>60</v>
       </c>
@@ -4632,7 +4635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>62</v>
       </c>
@@ -4702,7 +4705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>69</v>
       </c>
@@ -4737,7 +4740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>71</v>
       </c>
@@ -4772,7 +4775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>74</v>
       </c>
@@ -4807,7 +4810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>76</v>
       </c>
@@ -4842,7 +4845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>78</v>
       </c>
@@ -4877,7 +4880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>83</v>
       </c>
@@ -4912,7 +4915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>85</v>
       </c>
@@ -4947,7 +4950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>89</v>
       </c>
@@ -4982,7 +4985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>91</v>
       </c>
@@ -5017,7 +5020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>94</v>
       </c>
@@ -5052,7 +5055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>97</v>
       </c>
@@ -5087,7 +5090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>99</v>
       </c>
@@ -5122,7 +5125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>103</v>
       </c>
@@ -5157,7 +5160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>106</v>
       </c>
@@ -5196,18 +5199,6 @@
       <c r="D42" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K37" xr:uid="{1235A4A9-643F-403F-8F39-91437DA8F632}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="FALSE"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="10">
-      <filters>
-        <filter val="TRUE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5238,11 +5229,11 @@
         <v>161</v>
       </c>
       <c r="B3">
-        <f>COUNTIFS('Merged results table'!$E$1:$E$24,TRUE,'Merged results table'!$K$1:$K$24,TRUE)</f>
-        <v>19</v>
+        <f>COUNTIFS('Merged results table'!$E$1:$E$37,TRUE,'Merged results table'!$K$1:$K$37,TRUE)</f>
+        <v>30</v>
       </c>
       <c r="C3">
-        <f>COUNTIFS('Merged results table'!$E$1:$E$24,TRUE,'Merged results table'!$K$1:$K$24,FALSE)</f>
+        <f>COUNTIFS('Merged results table'!$E$1:$E$37,TRUE,'Merged results table'!$K$1:$K$37,FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -5251,12 +5242,12 @@
         <v>162</v>
       </c>
       <c r="B4">
-        <f>COUNTIFS('Merged results table'!$E$1:$E$24,FALSE,'Merged results table'!$K$1:$K$24,TRUE)</f>
+        <f>COUNTIFS('Merged results table'!$E$1:$E$37,FALSE,'Merged results table'!$K$1:$K$37,TRUE)</f>
         <v>3</v>
       </c>
       <c r="C4">
-        <f>COUNTIFS('Merged results table'!$E$1:$E$24,FALSE,'Merged results table'!$K$1:$K$24,FALSE)</f>
-        <v>1</v>
+        <f>COUNTIFS('Merged results table'!$E$1:$E$37,FALSE,'Merged results table'!$K$1:$K$37,FALSE)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
@@ -5265,7 +5256,7 @@
       </c>
       <c r="B6">
         <f>B3</f>
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -5274,7 +5265,7 @@
       </c>
       <c r="B7">
         <f>C4</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
@@ -5301,7 +5292,7 @@
       </c>
       <c r="B11">
         <f>(B3+C4)/(B3+B4+C3+C4)</f>
-        <v>0.86956521739130432</v>
+        <v>0.91666666666666663</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -5310,7 +5301,7 @@
       </c>
       <c r="B12">
         <f>B3/(B3+B4)</f>
-        <v>0.86363636363636365</v>
+        <v>0.90909090909090906</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
